--- a/file_upload_forms/040_government_business_license_submission_form--file_upload_forms.xlsx
+++ b/file_upload_forms/040_government_business_license_submission_form--file_upload_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -731,8 +731,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -760,12 +760,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sole_proprietorship'}</t>
+          <t>sole_proprietorship</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sole Proprietorship'}</t>
+          <t>Sole Proprietorship</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'partnership'}</t>
+          <t>partnership</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Partnership'}</t>
+          <t>Partnership</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'corporation'}</t>
+          <t>corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Corporation'}</t>
+          <t>Corporation</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'limited_liability_company_(llc)'}</t>
+          <t>limited_liability_company_(llc)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Limited Liability Company (LLC)'}</t>
+          <t>Limited Liability Company (LLC)</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'general_business_license'}</t>
+          <t>general_business_license</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'General Business License'}</t>
+          <t>General Business License</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'specialized_business_license'}</t>
+          <t>specialized_business_license</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Specialized Business License'}</t>
+          <t>Specialized Business License</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
